--- a/光伏配储项目/电价数据/2026/合和海风场陆上站.xlsx
+++ b/光伏配储项目/电价数据/2026/合和海风场陆上站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51002</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.52967</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5433600000000001</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.30186</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.31324</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.3035</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43847</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45529</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44027</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42361</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42012</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40922</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.3992</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40113</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38593</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42404</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41354</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35561</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39248</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38543</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41792</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41489</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42488</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41344</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44497</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.29986</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33297</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.25212</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29477</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.28246</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>-0.01733</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.11162</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>-0.03254</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.02476</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.0378</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08404</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.00697</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.1452</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21223</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23986</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.15075</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.0126</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.11983</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.01513</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.09125</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.25108</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.07079000000000001</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.18212</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.42963</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.17682</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.44666</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.06697</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.24912</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.5661799999999999</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.61203</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.21801</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.28502</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.28717</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.3781</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.28963</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.41294</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.4788</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.4003</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41189</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.421</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32998</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.43603</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.14803</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.69177</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.29724</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.79499</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53655</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5229299999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5063500000000001</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.46369</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49989</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.3732</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47373</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38098</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39214</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37655</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37651</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36051</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38143</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42247</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.51362</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.62379</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7251299999999999</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43602</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34619</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.12622</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.28765</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.16364</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.12088</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.25693</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.19383</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.14675</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.30874</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.12185</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.29126</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.15985</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>-0.00623</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.05589</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.11911</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.27408</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.1384</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.25496</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.20826</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.27572</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.29584</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>-0.006690000000000001</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>-0.04613</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.02838</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>-0.01857</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.23692</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.25845</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.36567</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.28596</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.2623</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.68763</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.78943</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.7746499999999999</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.79439</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.31129</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.47761</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.1354</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.44389</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.60441</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44033</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.4344</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40349</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.3767</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33316</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51638</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.37189</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48642</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38134</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40253</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.39378</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39094</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38257</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36189</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43429</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45071</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37164</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.3933</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36493</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35771</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36187</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37874</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47421</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45013</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44456</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34904</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39715</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35281</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36884</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.21073</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.29068</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.29688</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.30933</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>-0.0164</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.2639</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.24976</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30579</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.30885</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.29715</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.28467</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.33658</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.27141</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.25721</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.13292</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.08929999999999999</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.22748</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.27918</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.01663</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.16825</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29164</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.2984</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.27857</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.20013</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.15328</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>-0.00168</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.08287</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.05164</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.20141</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.27432</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.18493</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.25612</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.28312</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>-0.01146</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.0728</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.20326</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.2241</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.21018</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.05094</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.1391</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.08669</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.09673999999999999</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.23904</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.22127</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.27519</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3432</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.09319</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.24698</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.32312</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.28697</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.24761</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.34634</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.33477</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.30447</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.30498</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46888</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.30498</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.2975</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.29665</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.29437</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.29709</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.3905</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.3218</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.29926</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.24735</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.28312</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.2664</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.05168</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.004990000000000001</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>-0.03798</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>-0.00929</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.27963</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.23587</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.28339</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.27602</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.30697</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.38682</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.08498</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.12483</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.00529</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.04176</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.02727</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.27923</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.02815</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.09039</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>-0.02429</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.02624</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.16727</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.28494</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.28693</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.28046</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.03346</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.28961</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>-0.04998</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>-0.04822</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D121" t="n">
+        <v>-0.04815999999999999</v>
+      </c>
+      <c r="E121" t="n">
+        <v>-0.04553</v>
+      </c>
+      <c r="F121" t="n">
+        <v>-0.04786</v>
+      </c>
+      <c r="G121" t="n">
+        <v>-0.04815</v>
+      </c>
+      <c r="H121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J121" t="n">
+        <v>-0.03964</v>
+      </c>
+      <c r="K121" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="L121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X121" t="n">
+        <v>-0.04994</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>-0.04849000000000001</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>-0.0499</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.04381</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04972</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04983</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04935</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.04704999999999999</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>-0.04848</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.14909</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>-0.0499</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>-0.04151</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>-0.04999</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>-0.04813</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>-0.04999</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>-0.04999</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>-0.04994</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.25294</v>
+      </c>
+      <c r="D122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H122" t="n">
+        <v>-0.04949</v>
+      </c>
+      <c r="I122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J122" t="n">
+        <v>-0.04993</v>
+      </c>
+      <c r="K122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L122" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="N122" t="n">
+        <v>-0.04858</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.04947</v>
+      </c>
+      <c r="P122" t="n">
+        <v>-0.04967</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>-0.04924</v>
+      </c>
+      <c r="R122" t="n">
+        <v>-0.0488</v>
+      </c>
+      <c r="S122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U122" t="n">
+        <v>-0.04877</v>
+      </c>
+      <c r="V122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>-0.04998</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>-0.04998</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>-0.04999</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>-0.04999</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.0466</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04572</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04576</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04572</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04505</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04321</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04219</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04445</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.1014</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.0025</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04366</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04546</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04297</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04629999999999999</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04837</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04826</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04488</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04336</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04233</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04804</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04817</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04243</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04942</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04794</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04478</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04856</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04349</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.07256</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>-0.04998</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>-0.04953</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>-0.04998</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>-0.04959</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="C123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D123" t="n">
+        <v>-0.04778</v>
+      </c>
+      <c r="E123" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="F123" t="n">
+        <v>-0.04916</v>
+      </c>
+      <c r="G123" t="n">
+        <v>-0.04864</v>
+      </c>
+      <c r="H123" t="n">
+        <v>-0.04356</v>
+      </c>
+      <c r="I123" t="n">
+        <v>-0.04877</v>
+      </c>
+      <c r="J123" t="n">
+        <v>-0.04835</v>
+      </c>
+      <c r="K123" t="n">
+        <v>-0.04845</v>
+      </c>
+      <c r="L123" t="n">
+        <v>-0.04891</v>
+      </c>
+      <c r="M123" t="n">
+        <v>-0.04842</v>
+      </c>
+      <c r="N123" t="n">
+        <v>-0.04845</v>
+      </c>
+      <c r="O123" t="n">
+        <v>-0.04853</v>
+      </c>
+      <c r="P123" t="n">
+        <v>-0.04851</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>-0.0485</v>
+      </c>
+      <c r="R123" t="n">
+        <v>-0.04843</v>
+      </c>
+      <c r="S123" t="n">
+        <v>-0.04868</v>
+      </c>
+      <c r="T123" t="n">
+        <v>-0.04921</v>
+      </c>
+      <c r="U123" t="n">
+        <v>-0.04683</v>
+      </c>
+      <c r="V123" t="n">
+        <v>-0.04744</v>
+      </c>
+      <c r="W123" t="n">
+        <v>-0.04707</v>
+      </c>
+      <c r="X123" t="n">
+        <v>-0.04711</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>-0.04531</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>-0.04713000000000001</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>-0.0485</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>-0.04871</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>-0.04854</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>-0.04868</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>-0.04874</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>-0.04855</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>-0.04856</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>-0.04863</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>-0.04874</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>-0.04876</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>-0.04889</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>-0.04901</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.01832</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.12399</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.07614</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.00168</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.00214</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>-0.04995</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>-0.04987</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.4933999999999999</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.47876</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>0.9849</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>0.70355</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="C124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0.20636</v>
+      </c>
+      <c r="F124" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="G124" t="n">
+        <v>-0.04978</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6389400000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K124" t="n">
+        <v>-0.04933</v>
+      </c>
+      <c r="L124" t="n">
+        <v>-0.04923</v>
+      </c>
+      <c r="M124" t="n">
+        <v>-0.04953</v>
+      </c>
+      <c r="N124" t="n">
+        <v>-0.04898</v>
+      </c>
+      <c r="O124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P124" t="n">
+        <v>-0.04883</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>-0.04896</v>
+      </c>
+      <c r="R124" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="S124" t="n">
+        <v>-0.04921</v>
+      </c>
+      <c r="T124" t="n">
+        <v>-0.04907</v>
+      </c>
+      <c r="U124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V124" t="n">
+        <v>-0.04983</v>
+      </c>
+      <c r="W124" t="n">
+        <v>-0.04982</v>
+      </c>
+      <c r="X124" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>-0.04891</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>-0.04811</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>-0.04987</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>-0.04904</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>-0.04924</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>-0.04856</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>-0.0492</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58709</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42767</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>-0.04974</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>-0.04972</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.83212</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>-0.0126</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.01091</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.8359099999999999</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>-0.0498</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.10184</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>-0.04999</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.09551999999999999</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.14127</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>-0.04745000000000001</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>-0.04925</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>-0.04942</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>-0.04887</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45338</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>-0.04888</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>-0.04882</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>-0.04877</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>-0.04975</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>-0.04276</v>
+      </c>
+      <c r="C125" t="n">
+        <v>-0.04509000000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>-0.04923</v>
+      </c>
+      <c r="E125" t="n">
+        <v>-0.04915</v>
+      </c>
+      <c r="F125" t="n">
+        <v>-0.04543</v>
+      </c>
+      <c r="G125" t="n">
+        <v>-0.0492</v>
+      </c>
+      <c r="H125" t="n">
+        <v>-0.04624</v>
+      </c>
+      <c r="I125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J125" t="n">
+        <v>-0.04956</v>
+      </c>
+      <c r="K125" t="n">
+        <v>-0.04772</v>
+      </c>
+      <c r="L125" t="n">
+        <v>-0.04811</v>
+      </c>
+      <c r="M125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P125" t="n">
+        <v>-0.04942</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>-0.04939</v>
+      </c>
+      <c r="R125" t="n">
+        <v>-0.04922</v>
+      </c>
+      <c r="S125" t="n">
+        <v>-0.04895</v>
+      </c>
+      <c r="T125" t="n">
+        <v>-0.04916</v>
+      </c>
+      <c r="U125" t="n">
+        <v>-0.04996</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38767</v>
+      </c>
+      <c r="X125" t="n">
+        <v>-0.04944</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>-0.04949</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>-0.04971</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30161</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>-0.04955</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>-0.04875</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>-0.04834</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.0688</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.19664</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.30263</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>-0.03913000000000001</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.10345</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29292</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25559</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.27511</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.29964</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.20005</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.29745</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38881</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.37671</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43247</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.28681</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44782</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31972</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.4204</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59663</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.34277</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13916</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70255</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79396</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64883</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5827100000000001</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43956</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43711</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41476</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.3902</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42768</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39608</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.31119</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.29961</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.01207</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.1404</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.20239</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.20029</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.14911</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.20163</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>-0.00675</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.00675</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>-0.00675</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>-0.00315</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.00675</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>-0.00675</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.00675</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>-0.00377</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.00827</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.06469</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.0522</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>-0.00215</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>-0.00675</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>-0.00675</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.06246</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>-0.00087</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.08116</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.15831</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.16015</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.18349</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.20791</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.23799</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.27792</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.32252</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.19529</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.2836</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.30201</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.22569</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.20981</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.16022</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.17222</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.16913</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.16393</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.26261</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.17849</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.18784</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.18349</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.17477</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.16455</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.16882</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.16753</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.16696</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.15316</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.16875</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.16908</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.16316</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.18566</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.16142</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.16459</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.15344</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.16762</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.15438</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.15806</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.16321</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.22832</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.16941</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.1878</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.2598</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.21105</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.2157</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.18068</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.19766</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.17439</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.1788</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.16469</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.14404</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.20452</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.17664</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.16459</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.1598</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.15484</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.1447</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.08778</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.06570000000000001</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.09668</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.09813</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.05528</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.07329000000000001</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.03496</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.04577000000000001</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.13765</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.17105</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.18242</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.17609</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.20228</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.16727</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.20781</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.20259</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.18669</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.22129</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.18962</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.23792</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.20116</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.2239</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.28725</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.24217</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.25643</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.28087</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.27799</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.28206</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.27553</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.2315</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.23829</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.23291</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.1971</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.20315</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.18717</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.20721</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.26026</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.25528</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.2064</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.28555</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.29538</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.2336</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.24312</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.22506</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.20721</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.20721</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.20721</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.26844</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.2859</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.2703</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.22877</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.15698</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.26752</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.15849</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.29558</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.1578</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.07726000000000001</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.19719</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.12567</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.21071</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.15567</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.25755</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.21771</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.13153</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.25589</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.26714</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.30573</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.16684</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.24265</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.20537</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.26423</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.27169</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.27284</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.2783</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.26709</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.27914</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.29306</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.31736</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.27554</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.32384</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.30131</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.34643</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.1713</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.15321</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.20526</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.14129</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.22517</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.24307</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.29064</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.30012</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.35706</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.21257</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.30001</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.29159</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.20234</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.2878</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.2859</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.28869</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.28117</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.28264</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.27927</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.27905</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.20721</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.27169</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.28211</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.27346</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.21084</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.22318</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.27169</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.26695</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.26222</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.2752</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.26419</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.26506</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.32751</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.24327</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.27987</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.19084</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.37138</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.24327</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.23379</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.31785</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.21958</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.19589</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.21958</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.04759</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.24081</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.25937</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.23379</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.21958</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.18171</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.18486</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.19322</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.13812</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.25748</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.28969</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.20067</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.25674</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.2423</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.14612</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.13606</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.14079</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.1877</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.16075</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.18803</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.19256</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.19712</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.20202</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.14907</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.1486</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.30953</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.25152</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.21778</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.17711</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.12919</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.13352</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.14183</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.29755</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.22202</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.23442</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.17707</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.19421</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.19858</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.19708</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.11138</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.02864</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.17869</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.16777</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.12307</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.16137</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.19195</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.03836999999999999</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.26506</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.19491</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.19578</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.19447</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.26819</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.26506</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.27169</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.19375</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.26222</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.2625</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.26506</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.26819</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.27169</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.27643</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.2878</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.28117</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.28117</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.27614</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.27927</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.26243</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.26222</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.2752</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.28488</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.28969</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.27643</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.26819</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.26231</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.18926</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.19312</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.25937</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.2859</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.1886</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.29064</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.2893</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.18964</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.27485</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.23034</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.26819</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.26072</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.19277</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.26819</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.27018</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.2770899999999999</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.2954</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.2697</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.26222</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.26222</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.26222</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.25682</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.29064</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.25303</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.24924</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.2893</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.30012</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.28234</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.29064</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.30021</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.27255</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.27169</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.2135</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.31433</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.30021</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.30675</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.29532</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.30959</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.29064</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.21619</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.29064</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35582</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33968</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33673</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34861</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.28343</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31764</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32735</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.31383</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32639</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32222</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32905</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.57441</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.39094</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35464</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35471</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36591</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36234</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38094</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38351</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42962</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40898</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38598</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38548</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65138</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83314</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47275</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40679</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45936</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39338</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34483</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41152</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.3766</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.3717</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36382</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36084</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35685</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37089</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37954</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35821</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32312</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26178</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.13632</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.29414</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28445</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28307</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19633</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.2494</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27898</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>-0.04763000000000001</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.2794700000000001</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.12256</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28376</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.22548</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28668</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.2373</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.3039</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.30292</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14471</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29617</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.20017</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.2081</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.27819</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.28077</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.30011</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.29881</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.29041</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.32065</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.30167</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.41116</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.40123</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.64064</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.60525</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.5988600000000001</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.46086</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.62988</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.46049</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.41134</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.43377</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.4563</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37455</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35599</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.47879</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43064</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41965</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37504</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36017</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-0.03703</v>
+      </c>
+      <c r="D133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.43131</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.44193</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41953</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="K133" t="n">
+        <v>-0.03463</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="M133" t="n">
+        <v>-0.03476</v>
+      </c>
+      <c r="N133" t="n">
+        <v>-0.03489</v>
+      </c>
+      <c r="O133" t="n">
+        <v>-0.03478</v>
+      </c>
+      <c r="P133" t="n">
+        <v>-0.03441</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>-0.03444</v>
+      </c>
+      <c r="R133" t="n">
+        <v>-0.03427</v>
+      </c>
+      <c r="S133" t="n">
+        <v>-0.03429</v>
+      </c>
+      <c r="T133" t="n">
+        <v>-0.03417</v>
+      </c>
+      <c r="U133" t="n">
+        <v>-0.0347</v>
+      </c>
+      <c r="V133" t="n">
+        <v>-0.03447</v>
+      </c>
+      <c r="W133" t="n">
+        <v>-0.03465</v>
+      </c>
+      <c r="X133" t="n">
+        <v>-0.0347</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>-0.0346</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>-0.03489</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>-0.03428</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>-0.03508</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>-0.03447</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>-0.03424</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>-0.03432</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>-0.03707</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>-0.03541</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.23852</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.31409</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38428</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.36495</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.44254</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.17417</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>-0.02574</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>-0.01619</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.30733</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.36707</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.2735</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.22249</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.2733</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.09293000000000001</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>-0.04075</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.26966</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.27881</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.71453</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>-0.02189</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.24803</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.10783</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.0549</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.22673</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32641</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.30292</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>-0.03870000000000001</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>-0.03588</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>-0.03709</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>-0.03956</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>-0.03691</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.30272</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.31574</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.38343</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48352</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.36792</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.37266</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.37042</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.36829</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.37742</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.37196</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.43769</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.55892</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.7246699999999999</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.48008</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.5319700000000001</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.8136100000000001</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.74914</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.60033</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.64864</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.36639</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.40108</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.48141</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.37015</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.36876</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41944</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.40914</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.41536</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.42025</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45838</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43691</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42654</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44838</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41786</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45769</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39937</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40709</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39873</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38863</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37497</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37692</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37128</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38665</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36653</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36141</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.34467</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.34441</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.34473</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.34314</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36832</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.23819</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.25458</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.16945</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.22904</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.4126</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.04742</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.26351</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.39627</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.4174</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.4591</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.46388</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.48658</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.47459</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.31797</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31104</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.00226</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18904</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30264</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29289</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31816</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35266</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.34883</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.41035</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.35451</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.35533</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.37354</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.36383</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.36135</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.37823</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38551</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40587</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40115</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36513</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37806</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.37944</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37952</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35509</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38059</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.38379</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37899</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36409</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="E135" t="n">
+        <v>-0.03489</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.31499</v>
+      </c>
+      <c r="G135" t="n">
+        <v>-0.0217</v>
+      </c>
+      <c r="H135" t="n">
+        <v>-0.03907</v>
+      </c>
+      <c r="I135" t="n">
+        <v>-0.0342</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.36491</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-0.04017</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.33947</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.03348</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-0.03565</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33153</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="V135" t="n">
+        <v>-0.03457</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.33853</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>-0.03446</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-0.049</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>-0.04946</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>-0.049</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.04893</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>-0.03464</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>-0.04949</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>-0.0349</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.04874</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>-0.0497</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>-0.04995</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>-0.03507</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>-0.0249</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13034</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>-0.03526</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>-0.02417</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.14885</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04338</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.2553</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>-0.03715</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.14256</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.15162</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.00449</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30325</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.21607</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.22693</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.13904</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.21107</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.26518</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28329</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.25845</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.2969</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.28564</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.3117799999999999</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30684</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.34478</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.31728</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.34309</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.31664</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.34339</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34235</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.33993</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32312</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32392</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="I136" t="n">
+        <v>-0.0345</v>
+      </c>
+      <c r="J136" t="n">
+        <v>-0.03448</v>
+      </c>
+      <c r="K136" t="n">
+        <v>-0.0348</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.03421</v>
+      </c>
+      <c r="M136" t="n">
+        <v>-0.03461</v>
+      </c>
+      <c r="N136" t="n">
+        <v>-0.03468</v>
+      </c>
+      <c r="O136" t="n">
+        <v>-0.03467</v>
+      </c>
+      <c r="P136" t="n">
+        <v>-0.03405</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.03392</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.03399</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.03381</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.03397</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.03397</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.03388</v>
+      </c>
+      <c r="W136" t="n">
+        <v>-0.03443</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.03393</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.03397</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.03376</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>-0.03434</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.03371</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.0339</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>-0.03569</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.03463</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.03463</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>-0.03559</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.03701</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.04273</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.03305</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04217</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04889</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>-0.03597</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>-0.03598</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.26656</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.24357</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.24579</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.24554</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.25098</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.26438</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.28752</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.26958</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.25869</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.3037</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.27794</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.28239</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.26651</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.28178</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.26863</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.2847</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.27467</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.29543</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.30208</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.30649</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.28638</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.2575</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.26763</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.25309</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.2378</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.19265</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.05924</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29792</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.04093</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-0.03515</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.22878</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.22669</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.15135</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.27064</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.26434</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.24692</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.22423</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.20775</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.19128</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.21603</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.22658</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.17161</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.19181</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.2234</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.22366</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.24462</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.23317</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.21621</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.26433</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.22803</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.27082</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.31114</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.27218</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.24776</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.24946</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.18539</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.06849</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.5005299999999999</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.50449</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.51789</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.03890999999999999</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.19681</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.04217</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.19907</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.09995</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.0458</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.05226</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.00328</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.20865</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.03426</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.29174</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.0401</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.04432</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.02969</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.13282</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.03859000000000001</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.04466</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.0094</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.07861</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.02912</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>-0.00945</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.02898</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.05479</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.20297</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.26109</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.21935</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.24234</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.27011</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.27414</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.27101</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.29689</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.30801</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.27617</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.29657</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.29299</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.27745</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.30401</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.28052</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.30643</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.32726</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36402</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.29376</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.31154</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.31914</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.30235</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.31763</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.31341</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.31499</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.31447</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.31603</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.31091</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.31367</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.31442</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.31494</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.31484</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.31417</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.31408</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.31208</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.08701</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.31735</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.31728</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>-0.03401</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>-0.03525</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.29923</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.26382</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.36941</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.28286</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.37136</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.30738</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.29321</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.31239</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.27256</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31129</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.29065</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.28747</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.10293</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.2248</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26962</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30365</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.31279</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.14966</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.30688</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.14228</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.04814</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.30882</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.28992</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31024</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31641</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.31729</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.3157</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.31609</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.31691</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.31451</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.31324</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.31393</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.31481</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.3109</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.31726</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.3142</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>-0.04983</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.31103</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.31455</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.31389</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.31303</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31194</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>-0.0354</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>-0.03496</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>-0.03513</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>-0.03521</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>-0.035</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-0.04878</v>
+      </c>
+      <c r="D139" t="n">
+        <v>-0.04995</v>
+      </c>
+      <c r="E139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G139" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="H139" t="n">
+        <v>-0.0499</v>
+      </c>
+      <c r="I139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J139" t="n">
+        <v>-0.04981</v>
+      </c>
+      <c r="K139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M139" t="n">
+        <v>-0.04994</v>
+      </c>
+      <c r="N139" t="n">
+        <v>-0.04988</v>
+      </c>
+      <c r="O139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P139" t="n">
+        <v>-0.04999</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>-0.03498</v>
+      </c>
+      <c r="R139" t="n">
+        <v>-0.03477</v>
+      </c>
+      <c r="S139" t="n">
+        <v>-0.03441</v>
+      </c>
+      <c r="T139" t="n">
+        <v>-0.03459</v>
+      </c>
+      <c r="U139" t="n">
+        <v>-0.03352</v>
+      </c>
+      <c r="V139" t="n">
+        <v>-0.03476</v>
+      </c>
+      <c r="W139" t="n">
+        <v>-0.03488</v>
+      </c>
+      <c r="X139" t="n">
+        <v>-0.03477</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>-0.03562</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>-0.03482</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>-0.03478</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>-0.0347</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>-0.03436</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>-0.03469</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>-0.03634</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>-0.03556</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>-0.00012</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.30762</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.44999</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.3032</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.53001</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.09864000000000001</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>-0.00547</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>-0.00374</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>-0.00387</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>-0.00399</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.24907</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.23581</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>-0.03899</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>-0.04686999999999999</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>-0.03552</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>-0.04283</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>-0.03870000000000001</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>-0.03746</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>-0.03883</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34413</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36318</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32603</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>-0.03811999999999999</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.24649</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.26867</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.38863</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.37073</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.43876</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.4511</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.43043</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.44912</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.35214</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.37404</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.4171</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.29369</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.36392</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.4357200000000001</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>-0.00214</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38008</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.36767</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.00633</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.008119999999999999</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>-0.0009300000000000001</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.00675</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.00604</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.44946</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40101</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40105</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39165</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38076</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.3756</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37448</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.3786600000000001</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37737</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36921</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36695</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37109</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39969</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37583</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.31695</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.27747</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.07074</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.27241</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.00601</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.00331</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.00246</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.29372</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.10366</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.18531</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.31929</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.30235</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.30267</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29342</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.26937</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.28735</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.28088</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.17578</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33845</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.3146600000000001</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.15387</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.00495</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.00496</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.00276</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30666</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.28278</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.28604</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.30621</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.31318</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.4117</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.38646</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.36839</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.37287</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.44747</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5379299999999999</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.53351</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.35667</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.46611</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.5564199999999999</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.44526</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.31276</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.4546</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.50659</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.48748</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.7157100000000001</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.75817</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.5267000000000001</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.52858</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39838</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.37382</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37298</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37932</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.3752200000000001</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27129</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36987</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37066</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33776</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32122</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.34636</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.30566</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.2935</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.29363</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36361</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.29255</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.28781</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.28161</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.27599</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.31603</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.26581</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.27106</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.28347</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.21419</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.2401</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.14343</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>-0.00044</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.01628</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.2498</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.03175</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.03825</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.02147</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.00151</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.13294</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.12206</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.22094</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.19596</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.12312</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.2594</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.25792</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.30893</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.23073</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.3414700000000001</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.35057</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.29714</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.38009</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.39941</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.32258</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.31187</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38156</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.38248</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.29654</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.3943</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.34719</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.34846</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35086</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.78171</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.34506</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.34803</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.34893</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34264</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37967</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.34883</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.37942</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36331</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36421</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35597</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35102</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.32629</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.30287</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.30524</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.29767</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.2764</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.25219</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.23094</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.22128</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.19287</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.19062</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.19801</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.24769</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.07876999999999999</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>-0.00029</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>-0.007160000000000001</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>-0.006679999999999999</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.01908</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.10302</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.02483</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.0324</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.02756</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>-0.03313</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>-0.04281</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.02983</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.02995</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>-0.04171</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>-0.01432</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.13404</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>-0.01499</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.15844</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.17744</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.21656</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>-0.04278</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>-0.0151</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>-0.03327</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35928</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.44584</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.46276</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.41992</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.36449</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.53185</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.39336</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.45238</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.40036</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.39705</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.39693</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.4108</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.33491</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.3697</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.37568</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.39888</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.40028</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.38931</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35558</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.3502</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.50636</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.3999</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.31868</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35103</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.34726</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34771</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.37846</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.34726</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34283</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32109</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.34725</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34156</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.29474</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.25759</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.22259</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.20354</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.1337</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.18175</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.21803</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.2065</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.1251</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.13946</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.03049</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.10723</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.04064</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.04473</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>-0.04565</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.0454</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.03335</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.00558</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>-0.04037</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>-0.02623</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>-0.03641</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>-0.04252</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.06992</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>-0.04165</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>-0.04261</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>-0.04272</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.03621</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>-0.04017</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>-0.03947</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>-0.03623</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>-0.02892</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>-0.03925</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>-0.03942</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>-0.00911</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>-0.03051</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.18337</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.21706</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.24037</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.24683</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.25432</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.27034</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.27582</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.27744</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.3088399999999999</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.36989</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.40197</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35464</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.37078</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.38052</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.36238</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.3852</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.36481</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.36691</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.37072</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.36922</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.35874</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.36103</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.35864</v>
       </c>
     </row>
   </sheetData>
